--- a/Test Code/OneAsMany/d.xlsx
+++ b/Test Code/OneAsMany/d.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DropFleetTTS_Repo\DropfleetTTS\Test Code\OneAsMany Test\New\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DropFleetTTS_Repo\DropfleetTTS\Test Code\OneAsMany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEFF8380-2C2D-4495-96FF-053756E380A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD09F24-2C19-4079-92E2-A792D2B17C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="1410" windowWidth="33630" windowHeight="19245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40350" yWindow="195" windowWidth="25260" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ship Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5166" uniqueCount="1270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5252" uniqueCount="1286">
   <si>
     <t>Name</t>
   </si>
@@ -3846,6 +3846,54 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Stellargate_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>Aegis Platform</t>
+  </si>
+  <si>
+    <t>Comms Platform</t>
+  </si>
+  <si>
+    <t>Torpedo Platform</t>
+  </si>
+  <si>
+    <t>Aegis-4</t>
+  </si>
+  <si>
+    <t>Milwaukee</t>
+  </si>
+  <si>
+    <t>Rotterdam</t>
+  </si>
+  <si>
+    <t>New Dubai</t>
+  </si>
+  <si>
+    <t>Hong Kong</t>
+  </si>
+  <si>
+    <t>Siam</t>
+  </si>
+  <si>
+    <t>Yokohama</t>
+  </si>
+  <si>
+    <t>Busan</t>
+  </si>
+  <si>
+    <t>Guy Fawkes - Parliament</t>
+  </si>
+  <si>
+    <t>Fire Ship</t>
+  </si>
+  <si>
+    <t>Hero, Unique</t>
+  </si>
+  <si>
+    <t>The Hated - Little Chaos</t>
+  </si>
+  <si>
+    <t>Cloak-1, Hero, Stealth, Unique</t>
   </si>
 </sst>
 </file>
@@ -4205,7 +4253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R337"/>
+  <dimension ref="A1:R349"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -4220,8 +4268,8 @@
     <col min="11" max="12" width="5" customWidth="1"/>
     <col min="13" max="13" width="50" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
-    <col min="15" max="15" width="141.42578125" customWidth="1"/>
-    <col min="16" max="16" width="128.140625" customWidth="1"/>
+    <col min="15" max="15" width="39.7109375" customWidth="1"/>
+    <col min="16" max="16" width="35.42578125" customWidth="1"/>
     <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -20807,7 +20855,7 @@
         <v>1084</v>
       </c>
       <c r="B297">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="C297" t="s">
         <v>202</v>
@@ -20863,7 +20911,7 @@
         <v>1087</v>
       </c>
       <c r="B298">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C298" t="s">
         <v>202</v>
@@ -22914,10 +22962,10 @@
         <v>30</v>
       </c>
       <c r="E335">
+        <v>0</v>
+      </c>
+      <c r="F335">
         <v>8</v>
-      </c>
-      <c r="F335">
-        <v>0</v>
       </c>
       <c r="G335">
         <v>0</v>
@@ -22967,10 +23015,10 @@
         <v>30</v>
       </c>
       <c r="E336">
+        <v>0</v>
+      </c>
+      <c r="F336">
         <v>8</v>
-      </c>
-      <c r="F336">
-        <v>0</v>
       </c>
       <c r="G336">
         <v>0</v>
@@ -23020,10 +23068,10 @@
         <v>30</v>
       </c>
       <c r="E337">
+        <v>0</v>
+      </c>
+      <c r="F337">
         <v>8</v>
-      </c>
-      <c r="F337">
-        <v>0</v>
       </c>
       <c r="G337">
         <v>0</v>
@@ -23056,6 +23104,645 @@
         <v>1168</v>
       </c>
       <c r="R337" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="338" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D338">
+        <v>30</v>
+      </c>
+      <c r="E338">
+        <v>0</v>
+      </c>
+      <c r="F338">
+        <v>4</v>
+      </c>
+      <c r="G338">
+        <v>0</v>
+      </c>
+      <c r="H338">
+        <v>0</v>
+      </c>
+      <c r="I338">
+        <v>6</v>
+      </c>
+      <c r="J338">
+        <v>4</v>
+      </c>
+      <c r="K338">
+        <v>0</v>
+      </c>
+      <c r="L338">
+        <v>1</v>
+      </c>
+      <c r="M338" t="s">
+        <v>1273</v>
+      </c>
+      <c r="N338" t="s">
+        <v>946</v>
+      </c>
+      <c r="O338" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P338" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q338" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R338" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="339" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D339">
+        <v>30</v>
+      </c>
+      <c r="E339">
+        <v>0</v>
+      </c>
+      <c r="F339">
+        <v>8</v>
+      </c>
+      <c r="G339">
+        <v>0</v>
+      </c>
+      <c r="H339">
+        <v>0</v>
+      </c>
+      <c r="I339">
+        <v>5</v>
+      </c>
+      <c r="J339">
+        <v>5</v>
+      </c>
+      <c r="K339">
+        <v>0</v>
+      </c>
+      <c r="L339">
+        <v>1</v>
+      </c>
+      <c r="N339" t="s">
+        <v>946</v>
+      </c>
+      <c r="O339" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P339" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q339" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R339" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="340" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D340">
+        <v>30</v>
+      </c>
+      <c r="E340">
+        <v>0</v>
+      </c>
+      <c r="F340">
+        <v>8</v>
+      </c>
+      <c r="G340">
+        <v>0</v>
+      </c>
+      <c r="H340">
+        <v>0</v>
+      </c>
+      <c r="I340">
+        <v>5</v>
+      </c>
+      <c r="J340">
+        <v>5</v>
+      </c>
+      <c r="K340">
+        <v>0</v>
+      </c>
+      <c r="L340">
+        <v>1</v>
+      </c>
+      <c r="N340" t="s">
+        <v>946</v>
+      </c>
+      <c r="O340" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P340" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q340" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R340" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="341" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B341">
+        <v>225</v>
+      </c>
+      <c r="C341" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D341">
+        <v>50</v>
+      </c>
+      <c r="E341">
+        <v>7</v>
+      </c>
+      <c r="F341">
+        <v>8</v>
+      </c>
+      <c r="G341">
+        <v>6</v>
+      </c>
+      <c r="H341">
+        <v>15</v>
+      </c>
+      <c r="I341">
+        <v>4</v>
+      </c>
+      <c r="J341">
+        <v>3</v>
+      </c>
+      <c r="K341">
+        <v>5</v>
+      </c>
+      <c r="L341">
+        <v>1</v>
+      </c>
+      <c r="N341" t="s">
+        <v>946</v>
+      </c>
+      <c r="O341" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P341" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q341" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R341" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="342" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B342">
+        <v>195</v>
+      </c>
+      <c r="C342" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D342">
+        <v>50</v>
+      </c>
+      <c r="E342">
+        <v>7</v>
+      </c>
+      <c r="F342">
+        <v>8</v>
+      </c>
+      <c r="G342">
+        <v>6</v>
+      </c>
+      <c r="H342">
+        <v>15</v>
+      </c>
+      <c r="I342">
+        <v>4</v>
+      </c>
+      <c r="J342">
+        <v>3</v>
+      </c>
+      <c r="K342">
+        <v>5</v>
+      </c>
+      <c r="L342">
+        <v>1</v>
+      </c>
+      <c r="N342" t="s">
+        <v>946</v>
+      </c>
+      <c r="O342" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P342" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q342" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R342" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="343" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B343">
+        <v>215</v>
+      </c>
+      <c r="C343" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D343">
+        <v>50</v>
+      </c>
+      <c r="E343">
+        <v>7</v>
+      </c>
+      <c r="F343">
+        <v>8</v>
+      </c>
+      <c r="G343">
+        <v>6</v>
+      </c>
+      <c r="H343">
+        <v>15</v>
+      </c>
+      <c r="I343">
+        <v>4</v>
+      </c>
+      <c r="J343">
+        <v>3</v>
+      </c>
+      <c r="K343">
+        <v>5</v>
+      </c>
+      <c r="L343">
+        <v>1</v>
+      </c>
+      <c r="N343" t="s">
+        <v>946</v>
+      </c>
+      <c r="O343" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P343" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q343" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R343" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="344" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B344">
+        <v>185</v>
+      </c>
+      <c r="C344" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D344">
+        <v>50</v>
+      </c>
+      <c r="E344">
+        <v>7</v>
+      </c>
+      <c r="F344">
+        <v>8</v>
+      </c>
+      <c r="G344">
+        <v>6</v>
+      </c>
+      <c r="H344">
+        <v>15</v>
+      </c>
+      <c r="I344">
+        <v>4</v>
+      </c>
+      <c r="J344">
+        <v>3</v>
+      </c>
+      <c r="K344">
+        <v>5</v>
+      </c>
+      <c r="L344">
+        <v>1</v>
+      </c>
+      <c r="N344" t="s">
+        <v>946</v>
+      </c>
+      <c r="O344" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P344" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q344" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R344" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="345" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B345">
+        <v>180</v>
+      </c>
+      <c r="C345" t="s">
+        <v>202</v>
+      </c>
+      <c r="D345">
+        <v>50</v>
+      </c>
+      <c r="E345">
+        <v>8</v>
+      </c>
+      <c r="F345">
+        <v>8</v>
+      </c>
+      <c r="G345">
+        <v>6</v>
+      </c>
+      <c r="H345">
+        <v>14</v>
+      </c>
+      <c r="I345">
+        <v>4</v>
+      </c>
+      <c r="J345">
+        <v>3</v>
+      </c>
+      <c r="K345">
+        <v>6</v>
+      </c>
+      <c r="L345">
+        <v>1</v>
+      </c>
+      <c r="N345" t="s">
+        <v>946</v>
+      </c>
+      <c r="O345" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P345" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q345" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R345" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="346" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B346">
+        <v>160</v>
+      </c>
+      <c r="C346" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D346">
+        <v>50</v>
+      </c>
+      <c r="E346">
+        <v>7</v>
+      </c>
+      <c r="F346">
+        <v>8</v>
+      </c>
+      <c r="G346">
+        <v>6</v>
+      </c>
+      <c r="H346">
+        <v>13</v>
+      </c>
+      <c r="I346">
+        <v>4</v>
+      </c>
+      <c r="J346">
+        <v>3</v>
+      </c>
+      <c r="K346">
+        <v>6</v>
+      </c>
+      <c r="L346">
+        <v>1</v>
+      </c>
+      <c r="N346" t="s">
+        <v>946</v>
+      </c>
+      <c r="O346" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P346" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q346" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R346" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="347" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B347">
+        <v>166</v>
+      </c>
+      <c r="C347" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D347">
+        <v>50</v>
+      </c>
+      <c r="E347">
+        <v>7</v>
+      </c>
+      <c r="F347">
+        <v>8</v>
+      </c>
+      <c r="G347">
+        <v>6</v>
+      </c>
+      <c r="H347">
+        <v>13</v>
+      </c>
+      <c r="I347">
+        <v>4</v>
+      </c>
+      <c r="J347">
+        <v>3</v>
+      </c>
+      <c r="K347">
+        <v>6</v>
+      </c>
+      <c r="L347">
+        <v>1</v>
+      </c>
+      <c r="N347" t="s">
+        <v>946</v>
+      </c>
+      <c r="O347" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P347" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q347" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R347" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="348" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B348">
+        <v>85</v>
+      </c>
+      <c r="C348" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D348">
+        <v>40</v>
+      </c>
+      <c r="E348">
+        <v>9</v>
+      </c>
+      <c r="F348">
+        <v>6</v>
+      </c>
+      <c r="G348">
+        <v>4</v>
+      </c>
+      <c r="H348">
+        <v>6</v>
+      </c>
+      <c r="I348">
+        <v>2</v>
+      </c>
+      <c r="J348">
+        <v>2</v>
+      </c>
+      <c r="K348">
+        <v>6</v>
+      </c>
+      <c r="L348">
+        <v>1</v>
+      </c>
+      <c r="M348" t="s">
+        <v>1283</v>
+      </c>
+      <c r="N348" t="s">
+        <v>482</v>
+      </c>
+      <c r="O348" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P348" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q348" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R348" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="349" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C349" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D349">
+        <v>30</v>
+      </c>
+      <c r="E349">
+        <v>10</v>
+      </c>
+      <c r="F349">
+        <v>6</v>
+      </c>
+      <c r="G349">
+        <v>5</v>
+      </c>
+      <c r="H349">
+        <v>8</v>
+      </c>
+      <c r="I349">
+        <v>4</v>
+      </c>
+      <c r="J349">
+        <v>5</v>
+      </c>
+      <c r="K349">
+        <v>6</v>
+      </c>
+      <c r="L349">
+        <v>1</v>
+      </c>
+      <c r="M349" t="s">
+        <v>1285</v>
+      </c>
+      <c r="N349" t="s">
+        <v>626</v>
+      </c>
+      <c r="O349" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P349" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q349" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R349" t="s">
         <v>1168</v>
       </c>
     </row>

--- a/Test Code/OneAsMany/d.xlsx
+++ b/Test Code/OneAsMany/d.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DropFleetTTS_Repo\DropfleetTTS\Test Code\OneAsMany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD09F24-2C19-4079-92E2-A792D2B17C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FF0136-AB6E-4B9D-B470-DEA6B687702E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40350" yWindow="195" windowWidth="25260" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1230" yWindow="2430" windowWidth="38820" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ship Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5252" uniqueCount="1286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5253" uniqueCount="1310">
   <si>
     <t>Name</t>
   </si>
@@ -3894,6 +3894,78 @@
   </si>
   <si>
     <t>Cloak-1, Hero, Stealth, Unique</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Aegis Platform_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Aegis Platform_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Comms Platform_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Comms Platform_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Torpedo Platform_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Torpedo Platform_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Milwaukee_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Milwaukee_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Rotterdam_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Rotterdam_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/New Dubai_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/New Dubai_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Hong Kong_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Hong Kong_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Siam_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Siam_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Yokohama_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Yokohama_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Busan_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Busan_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/RES/Guy Fawkes - Parliament_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/RES/Guy Fawkes - Parliament_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/The Hated - Little Chaos_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/The Hated - Little Chaos_CardFrontImage.png</t>
   </si>
 </sst>
 </file>
@@ -4268,8 +4340,8 @@
     <col min="11" max="12" width="5" customWidth="1"/>
     <col min="13" max="13" width="50" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
-    <col min="15" max="15" width="39.7109375" customWidth="1"/>
-    <col min="16" max="16" width="35.42578125" customWidth="1"/>
+    <col min="15" max="15" width="133.28515625" customWidth="1"/>
+    <col min="16" max="16" width="131.140625" customWidth="1"/>
     <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -22219,7 +22291,7 @@
       <c r="O321" t="s">
         <v>1225</v>
       </c>
-      <c r="P321" t="s">
+      <c r="P321" s="2" t="s">
         <v>1226</v>
       </c>
       <c r="Q321" t="s">
@@ -23151,10 +23223,10 @@
         <v>946</v>
       </c>
       <c r="O338" t="s">
-        <v>1268</v>
+        <v>1286</v>
       </c>
       <c r="P338" t="s">
-        <v>1269</v>
+        <v>1287</v>
       </c>
       <c r="Q338" t="s">
         <v>1168</v>
@@ -23204,10 +23276,10 @@
         <v>946</v>
       </c>
       <c r="O339" t="s">
-        <v>1268</v>
+        <v>1288</v>
       </c>
       <c r="P339" t="s">
-        <v>1269</v>
+        <v>1289</v>
       </c>
       <c r="Q339" t="s">
         <v>1168</v>
@@ -23257,10 +23329,10 @@
         <v>946</v>
       </c>
       <c r="O340" t="s">
-        <v>1268</v>
+        <v>1290</v>
       </c>
       <c r="P340" t="s">
-        <v>1269</v>
+        <v>1291</v>
       </c>
       <c r="Q340" t="s">
         <v>1168</v>
@@ -23310,10 +23382,10 @@
         <v>946</v>
       </c>
       <c r="O341" t="s">
-        <v>1268</v>
+        <v>1292</v>
       </c>
       <c r="P341" t="s">
-        <v>1269</v>
+        <v>1293</v>
       </c>
       <c r="Q341" t="s">
         <v>1168</v>
@@ -23363,10 +23435,10 @@
         <v>946</v>
       </c>
       <c r="O342" t="s">
-        <v>1268</v>
+        <v>1294</v>
       </c>
       <c r="P342" t="s">
-        <v>1269</v>
+        <v>1295</v>
       </c>
       <c r="Q342" t="s">
         <v>1168</v>
@@ -23416,10 +23488,10 @@
         <v>946</v>
       </c>
       <c r="O343" t="s">
-        <v>1268</v>
+        <v>1296</v>
       </c>
       <c r="P343" t="s">
-        <v>1269</v>
+        <v>1297</v>
       </c>
       <c r="Q343" t="s">
         <v>1168</v>
@@ -23469,10 +23541,10 @@
         <v>946</v>
       </c>
       <c r="O344" t="s">
-        <v>1268</v>
+        <v>1298</v>
       </c>
       <c r="P344" t="s">
-        <v>1269</v>
+        <v>1299</v>
       </c>
       <c r="Q344" t="s">
         <v>1168</v>
@@ -23522,10 +23594,10 @@
         <v>946</v>
       </c>
       <c r="O345" t="s">
-        <v>1268</v>
+        <v>1300</v>
       </c>
       <c r="P345" t="s">
-        <v>1269</v>
+        <v>1301</v>
       </c>
       <c r="Q345" t="s">
         <v>1168</v>
@@ -23575,10 +23647,10 @@
         <v>946</v>
       </c>
       <c r="O346" t="s">
-        <v>1268</v>
+        <v>1302</v>
       </c>
       <c r="P346" t="s">
-        <v>1269</v>
+        <v>1303</v>
       </c>
       <c r="Q346" t="s">
         <v>1168</v>
@@ -23628,10 +23700,10 @@
         <v>946</v>
       </c>
       <c r="O347" t="s">
-        <v>1268</v>
+        <v>1304</v>
       </c>
       <c r="P347" t="s">
-        <v>1269</v>
+        <v>1305</v>
       </c>
       <c r="Q347" t="s">
         <v>1168</v>
@@ -23684,10 +23756,10 @@
         <v>482</v>
       </c>
       <c r="O348" t="s">
-        <v>1268</v>
+        <v>1306</v>
       </c>
       <c r="P348" t="s">
-        <v>1269</v>
+        <v>1307</v>
       </c>
       <c r="Q348" t="s">
         <v>1168</v>
@@ -23697,8 +23769,14 @@
       </c>
     </row>
     <row r="349" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B349">
+        <v>90</v>
+      </c>
       <c r="C349" t="s">
-        <v>1284</v>
+        <v>1024</v>
       </c>
       <c r="D349">
         <v>30</v>
@@ -23734,10 +23812,10 @@
         <v>626</v>
       </c>
       <c r="O349" t="s">
-        <v>1268</v>
+        <v>1308</v>
       </c>
       <c r="P349" t="s">
-        <v>1269</v>
+        <v>1309</v>
       </c>
       <c r="Q349" t="s">
         <v>1168</v>
@@ -23783,6 +23861,7 @@
     <hyperlink ref="P313" r:id="rId33" xr:uid="{2E843717-98E6-48B0-8415-7A7747E50455}"/>
     <hyperlink ref="O311" r:id="rId34" xr:uid="{C3048C77-C426-4CAD-9EBB-AD0D20C3AE7B}"/>
     <hyperlink ref="O325" r:id="rId35" xr:uid="{DE2F7D83-9AEF-45C0-BC31-FEBEFD8A07DE}"/>
+    <hyperlink ref="P321" r:id="rId36" xr:uid="{02117735-8EBF-4917-BE94-6ADA5B7F51C3}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Test Code/OneAsMany/d.xlsx
+++ b/Test Code/OneAsMany/d.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DropFleetTTS_Repo\DropfleetTTS\Test Code\OneAsMany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C8C372-C33E-43AE-98CF-4D757F134A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8E59D9-1CA6-4FBE-90F1-BD88471453DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3890,9 +3890,6 @@
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/The Hated - Little Chaos_ModelImage.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/The Hated - Little Chaos_CardFrontImage.png</t>
-  </si>
-  <si>
     <t>Anode - The Melter</t>
   </si>
   <si>
@@ -3950,81 +3947,42 @@
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Anode - The Melter_ModelImage.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Anode - The Melter_ModelImage.png/93_CardFrontImage.png</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/OBV-64 Oblivion Barge_ModelImage.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/OBV-64 Oblivion Barge_ModelImage.png/125_CardFrontImage.png</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/PRK-91 Provenance Ark_ModelImage.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/PRK-91 Provenance Ark_ModelImage.png/410_CardFrontImage.png</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Scanner Tower_ModelImage.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Scanner Tower_ModelImage.png/0_CardFrontImage.png</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Shield Platform_ModelImage.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Shield Platform_ModelImage.png/0_CardFrontImage.png</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Heavy Calibre Orbital Gun_ModelImage.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Heavy Calibre Orbital Gun_ModelImage.png/0_CardFrontImage.png</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Leonnatus_ModelImage.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Leonnatus_ModelImage.png/190_CardFrontImage.png</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Antigonus_ModelImage.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Antigonus_ModelImage.png/176_CardFrontImage.png</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Seleucus_ModelImage.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Seleucus_ModelImage.png/200_CardFrontImage.png</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Ptolemy_ModelImage.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Ptolemy_ModelImage.png/174_CardFrontImage.png</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Antony_ModelImage.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Antony_ModelImage.png/200_CardFrontImage.png</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Cato_ModelImage.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Cato_ModelImage.png/185_CardFrontImage.png</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Brutus_ModelImage.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Brutus_ModelImage.png/210_CardFrontImage.png</t>
-  </si>
-  <si>
     <t>Atlas</t>
   </si>
   <si>
@@ -4095,6 +4053,48 @@
   </si>
   <si>
     <t>“Granite” Halsey</t>
+  </si>
+  <si>
+    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/The Hated - Little Chaos_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Anode - The Melter_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/OBV-64 Oblivion Barge_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/PRK-91 Provenance Ark_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Scanner Tower_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Shield Platform_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Heavy Calibre Orbital Gun_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Leonnatus_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Antigonus_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Seleucus_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Ptolemy_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Antony_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Cato_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Brutus_CardFrontImage.png</t>
   </si>
 </sst>
 </file>
@@ -4589,7 +4589,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1329</v>
+        <v>1315</v>
       </c>
       <c r="B3">
         <v>155</v>
@@ -4645,7 +4645,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1331</v>
+        <v>1317</v>
       </c>
       <c r="B4">
         <v>195</v>
@@ -4701,7 +4701,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1332</v>
+        <v>1318</v>
       </c>
       <c r="B5">
         <v>310</v>
@@ -4757,7 +4757,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1330</v>
+        <v>1316</v>
       </c>
       <c r="B6">
         <v>520</v>
@@ -8285,7 +8285,7 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1333</v>
+        <v>1319</v>
       </c>
       <c r="B69">
         <v>207</v>
@@ -8341,7 +8341,7 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1334</v>
+        <v>1320</v>
       </c>
       <c r="B70">
         <v>200</v>
@@ -8397,7 +8397,7 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1335</v>
+        <v>1321</v>
       </c>
       <c r="B71">
         <v>310</v>
@@ -8453,7 +8453,7 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1336</v>
+        <v>1322</v>
       </c>
       <c r="B72">
         <v>555</v>
@@ -11253,7 +11253,7 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>1337</v>
+        <v>1323</v>
       </c>
       <c r="B122">
         <v>158</v>
@@ -11309,7 +11309,7 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>1338</v>
+        <v>1324</v>
       </c>
       <c r="B123">
         <v>255</v>
@@ -11365,7 +11365,7 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>1339</v>
+        <v>1325</v>
       </c>
       <c r="B124">
         <v>415</v>
@@ -11421,7 +11421,7 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>1340</v>
+        <v>1326</v>
       </c>
       <c r="B125">
         <v>570</v>
@@ -13437,7 +13437,7 @@
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>1341</v>
+        <v>1327</v>
       </c>
       <c r="B161">
         <v>170</v>
@@ -13493,7 +13493,7 @@
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>1342</v>
+        <v>1328</v>
       </c>
       <c r="B162">
         <v>285</v>
@@ -13549,7 +13549,7 @@
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>1343</v>
+        <v>1329</v>
       </c>
       <c r="B163">
         <v>265</v>
@@ -13605,7 +13605,7 @@
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>1344</v>
+        <v>1330</v>
       </c>
       <c r="B164">
         <v>575</v>
@@ -16069,7 +16069,7 @@
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>1345</v>
+        <v>1331</v>
       </c>
       <c r="B208">
         <v>245</v>
@@ -16125,7 +16125,7 @@
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>1346</v>
+        <v>1332</v>
       </c>
       <c r="B209">
         <v>195</v>
@@ -16181,7 +16181,7 @@
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>1347</v>
+        <v>1333</v>
       </c>
       <c r="B210">
         <v>295</v>
@@ -16237,7 +16237,7 @@
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>1348</v>
+        <v>1334</v>
       </c>
       <c r="B211">
         <v>495</v>
@@ -18813,7 +18813,7 @@
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1349</v>
+        <v>1335</v>
       </c>
       <c r="B257">
         <v>155</v>
@@ -18869,7 +18869,7 @@
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>1350</v>
+        <v>1336</v>
       </c>
       <c r="B258">
         <v>220</v>
@@ -18925,7 +18925,7 @@
     </row>
     <row r="259" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>1351</v>
+        <v>1337</v>
       </c>
       <c r="B259">
         <v>330</v>
@@ -18981,7 +18981,7 @@
     </row>
     <row r="260" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>1352</v>
+        <v>1338</v>
       </c>
       <c r="B260">
         <v>635</v>
@@ -23944,7 +23944,7 @@
         <v>1283</v>
       </c>
       <c r="P349" s="2" t="s">
-        <v>1284</v>
+        <v>1339</v>
       </c>
       <c r="Q349" t="s">
         <v>1143</v>
@@ -23955,7 +23955,7 @@
     </row>
     <row r="350" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B350">
         <v>93</v>
@@ -23996,11 +23996,11 @@
       <c r="N350" t="s">
         <v>16</v>
       </c>
-      <c r="O350" t="s">
-        <v>1303</v>
-      </c>
-      <c r="P350" t="s">
-        <v>1304</v>
+      <c r="O350" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="P350" s="2" t="s">
+        <v>1340</v>
       </c>
       <c r="Q350" t="s">
         <v>1143</v>
@@ -24011,13 +24011,13 @@
     </row>
     <row r="351" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B351">
         <v>125</v>
       </c>
       <c r="C351" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D351">
         <v>40</v>
@@ -24047,16 +24047,16 @@
         <v>1</v>
       </c>
       <c r="M351" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="N351" t="s">
         <v>237</v>
       </c>
       <c r="O351" t="s">
-        <v>1305</v>
-      </c>
-      <c r="P351" t="s">
-        <v>1306</v>
+        <v>1303</v>
+      </c>
+      <c r="P351" s="2" t="s">
+        <v>1341</v>
       </c>
       <c r="Q351" t="s">
         <v>1143</v>
@@ -24067,13 +24067,13 @@
     </row>
     <row r="352" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B352">
         <v>410</v>
       </c>
       <c r="C352" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="D352">
         <v>60</v>
@@ -24103,16 +24103,16 @@
         <v>1</v>
       </c>
       <c r="M352" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="N352" t="s">
         <v>237</v>
       </c>
-      <c r="O352" t="s">
-        <v>1307</v>
-      </c>
-      <c r="P352" t="s">
-        <v>1308</v>
+      <c r="O352" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="P352" s="2" t="s">
+        <v>1342</v>
       </c>
       <c r="Q352" t="s">
         <v>1143</v>
@@ -24123,7 +24123,7 @@
     </row>
     <row r="353" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B353">
         <v>0</v>
@@ -24162,10 +24162,10 @@
         <v>295</v>
       </c>
       <c r="O353" t="s">
-        <v>1309</v>
-      </c>
-      <c r="P353" t="s">
-        <v>1310</v>
+        <v>1305</v>
+      </c>
+      <c r="P353" s="2" t="s">
+        <v>1343</v>
       </c>
       <c r="Q353" t="s">
         <v>1143</v>
@@ -24176,7 +24176,7 @@
     </row>
     <row r="354" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B354">
         <v>0</v>
@@ -24215,10 +24215,10 @@
         <v>295</v>
       </c>
       <c r="O354" t="s">
-        <v>1311</v>
-      </c>
-      <c r="P354" t="s">
-        <v>1312</v>
+        <v>1306</v>
+      </c>
+      <c r="P354" s="2" t="s">
+        <v>1344</v>
       </c>
       <c r="Q354" t="s">
         <v>1143</v>
@@ -24229,7 +24229,7 @@
     </row>
     <row r="355" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B355">
         <v>0</v>
@@ -24268,10 +24268,10 @@
         <v>295</v>
       </c>
       <c r="O355" t="s">
-        <v>1313</v>
-      </c>
-      <c r="P355" t="s">
-        <v>1314</v>
+        <v>1307</v>
+      </c>
+      <c r="P355" s="2" t="s">
+        <v>1345</v>
       </c>
       <c r="Q355" t="s">
         <v>1143</v>
@@ -24282,7 +24282,7 @@
     </row>
     <row r="356" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B356">
         <v>190</v>
@@ -24321,10 +24321,10 @@
         <v>295</v>
       </c>
       <c r="O356" t="s">
-        <v>1315</v>
-      </c>
-      <c r="P356" t="s">
-        <v>1316</v>
+        <v>1308</v>
+      </c>
+      <c r="P356" s="2" t="s">
+        <v>1346</v>
       </c>
       <c r="Q356" t="s">
         <v>1143</v>
@@ -24335,7 +24335,7 @@
     </row>
     <row r="357" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B357">
         <v>176</v>
@@ -24371,16 +24371,16 @@
         <v>1</v>
       </c>
       <c r="M357" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="N357" t="s">
         <v>295</v>
       </c>
       <c r="O357" t="s">
-        <v>1317</v>
-      </c>
-      <c r="P357" t="s">
-        <v>1318</v>
+        <v>1309</v>
+      </c>
+      <c r="P357" s="2" t="s">
+        <v>1347</v>
       </c>
       <c r="Q357" t="s">
         <v>1143</v>
@@ -24391,7 +24391,7 @@
     </row>
     <row r="358" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B358">
         <v>190</v>
@@ -24430,10 +24430,10 @@
         <v>295</v>
       </c>
       <c r="O358" t="s">
-        <v>1315</v>
-      </c>
-      <c r="P358" t="s">
-        <v>1316</v>
+        <v>1308</v>
+      </c>
+      <c r="P358" s="2" t="s">
+        <v>1346</v>
       </c>
       <c r="Q358" t="s">
         <v>1143</v>
@@ -24444,7 +24444,7 @@
     </row>
     <row r="359" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B359">
         <v>200</v>
@@ -24483,10 +24483,10 @@
         <v>295</v>
       </c>
       <c r="O359" t="s">
-        <v>1319</v>
-      </c>
-      <c r="P359" t="s">
-        <v>1320</v>
+        <v>1310</v>
+      </c>
+      <c r="P359" s="2" t="s">
+        <v>1348</v>
       </c>
       <c r="Q359" t="s">
         <v>1143</v>
@@ -24497,7 +24497,7 @@
     </row>
     <row r="360" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B360">
         <v>174</v>
@@ -24536,10 +24536,10 @@
         <v>295</v>
       </c>
       <c r="O360" t="s">
-        <v>1321</v>
-      </c>
-      <c r="P360" t="s">
-        <v>1322</v>
+        <v>1311</v>
+      </c>
+      <c r="P360" s="2" t="s">
+        <v>1349</v>
       </c>
       <c r="Q360" t="s">
         <v>1143</v>
@@ -24550,7 +24550,7 @@
     </row>
     <row r="361" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B361">
         <v>200</v>
@@ -24589,10 +24589,10 @@
         <v>295</v>
       </c>
       <c r="O361" t="s">
-        <v>1323</v>
-      </c>
-      <c r="P361" t="s">
-        <v>1324</v>
+        <v>1312</v>
+      </c>
+      <c r="P361" s="2" t="s">
+        <v>1350</v>
       </c>
       <c r="Q361" t="s">
         <v>1143</v>
@@ -24603,7 +24603,7 @@
     </row>
     <row r="362" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B362">
         <v>185</v>
@@ -24642,10 +24642,10 @@
         <v>295</v>
       </c>
       <c r="O362" t="s">
-        <v>1325</v>
-      </c>
-      <c r="P362" t="s">
-        <v>1326</v>
+        <v>1313</v>
+      </c>
+      <c r="P362" s="2" t="s">
+        <v>1351</v>
       </c>
       <c r="Q362" t="s">
         <v>1143</v>
@@ -24656,7 +24656,7 @@
     </row>
     <row r="363" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B363">
         <v>210</v>
@@ -24695,10 +24695,10 @@
         <v>295</v>
       </c>
       <c r="O363" t="s">
-        <v>1327</v>
-      </c>
-      <c r="P363" t="s">
-        <v>1328</v>
+        <v>1314</v>
+      </c>
+      <c r="P363" s="2" t="s">
+        <v>1352</v>
       </c>
       <c r="Q363" t="s">
         <v>1143</v>
@@ -24746,7 +24746,11 @@
     <hyperlink ref="O325" r:id="rId35" xr:uid="{DE2F7D83-9AEF-45C0-BC31-FEBEFD8A07DE}"/>
     <hyperlink ref="P321" r:id="rId36" xr:uid="{02117735-8EBF-4917-BE94-6ADA5B7F51C3}"/>
     <hyperlink ref="O349" r:id="rId37" xr:uid="{0391698A-2426-4118-8FD5-B4AF7E613286}"/>
-    <hyperlink ref="P349" r:id="rId38" xr:uid="{E9767834-A49F-47F2-AF9F-55B221D57C59}"/>
+    <hyperlink ref="P349" r:id="rId38" display="https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/The Hated - Little Chaos_CardFrontImage.png" xr:uid="{E9767834-A49F-47F2-AF9F-55B221D57C59}"/>
+    <hyperlink ref="P350" r:id="rId39" display="https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips//BIO/Anode - The Melter_CardFrontImage.png" xr:uid="{01F86FA8-D3B1-47E3-A22B-9BCE334EB3FE}"/>
+    <hyperlink ref="O350" r:id="rId40" xr:uid="{E4D87E9E-ECDF-4D05-9366-677CBA028E23}"/>
+    <hyperlink ref="P351:P363" r:id="rId41" display="https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Anode - The Melter_ModelImage.png" xr:uid="{3CC59D09-23DB-4265-BAD0-94C03FC344FF}"/>
+    <hyperlink ref="O352" r:id="rId42" xr:uid="{E8A9C9F7-8738-4A01-9CB8-A521C52E00EB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Test Code/OneAsMany/d.xlsx
+++ b/Test Code/OneAsMany/d.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DropFleetTTS_Repo\DropfleetTTS\Test Code\OneAsMany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8E59D9-1CA6-4FBE-90F1-BD88471453DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FEDE5B8-A30C-4CFE-9B44-DB49FDADDFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1845" yWindow="1095" windowWidth="30165" windowHeight="19350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ship Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5355" uniqueCount="1353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5420" uniqueCount="1381">
   <si>
     <t>Name</t>
   </si>
@@ -3950,151 +3950,235 @@
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/OBV-64 Oblivion Barge_ModelImage.png</t>
   </si>
   <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Scanner Tower_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Shield Platform_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Heavy Calibre Orbital Gun_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Leonnatus_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Antigonus_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Seleucus_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Ptolemy_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Antony_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Cato_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Brutus_ModelImage.png</t>
+  </si>
+  <si>
+    <t>Atlas</t>
+  </si>
+  <si>
+    <t>Ascendant</t>
+  </si>
+  <si>
+    <t>Atom</t>
+  </si>
+  <si>
+    <t>Agency</t>
+  </si>
+  <si>
+    <t>Javelin</t>
+  </si>
+  <si>
+    <t>Helena of Asgard</t>
+  </si>
+  <si>
+    <t>Claudia Rhee</t>
+  </si>
+  <si>
+    <t>Gaius Chau</t>
+  </si>
+  <si>
+    <t>Typhoon Vasquez</t>
+  </si>
+  <si>
+    <t>Hagen</t>
+  </si>
+  <si>
+    <t>Nguen</t>
+  </si>
+  <si>
+    <t>Magellan</t>
+  </si>
+  <si>
+    <t>Enslaver</t>
+  </si>
+  <si>
+    <t>Flayer</t>
+  </si>
+  <si>
+    <t>Baba Yaga</t>
+  </si>
+  <si>
+    <t>Overlord of Flies</t>
+  </si>
+  <si>
+    <t>Twins of Aaru</t>
+  </si>
+  <si>
+    <t>Seth</t>
+  </si>
+  <si>
+    <t>Mergen the Learned</t>
+  </si>
+  <si>
+    <t>Quetzalcoatl</t>
+  </si>
+  <si>
+    <t>Tayne</t>
+  </si>
+  <si>
+    <t>Weaver</t>
+  </si>
+  <si>
+    <t>Havelock</t>
+  </si>
+  <si>
+    <t>“Granite” Halsey</t>
+  </si>
+  <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/PRK-91 Provenance Ark_ModelImage.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Scanner Tower_ModelImage.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Shield Platform_ModelImage.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Heavy Calibre Orbital Gun_ModelImage.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Leonnatus_ModelImage.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Antigonus_ModelImage.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Seleucus_ModelImage.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Ptolemy_ModelImage.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Antony_ModelImage.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Cato_ModelImage.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Brutus_ModelImage.png</t>
-  </si>
-  <si>
-    <t>Atlas</t>
-  </si>
-  <si>
-    <t>Ascendant</t>
-  </si>
-  <si>
-    <t>Atom</t>
-  </si>
-  <si>
-    <t>Agency</t>
-  </si>
-  <si>
-    <t>Javelin</t>
-  </si>
-  <si>
-    <t>Helena of Asgard</t>
-  </si>
-  <si>
-    <t>Claudia Rhee</t>
-  </si>
-  <si>
-    <t>Gaius Chau</t>
-  </si>
-  <si>
-    <t>Typhoon Vasquez</t>
-  </si>
-  <si>
-    <t>Hagen</t>
-  </si>
-  <si>
-    <t>Nguen</t>
-  </si>
-  <si>
-    <t>Magellan</t>
-  </si>
-  <si>
-    <t>Enslaver</t>
-  </si>
-  <si>
-    <t>Flayer</t>
-  </si>
-  <si>
-    <t>Baba Yaga</t>
-  </si>
-  <si>
-    <t>Overlord of Flies</t>
-  </si>
-  <si>
-    <t>Twins of Aaru</t>
-  </si>
-  <si>
-    <t>Seth</t>
-  </si>
-  <si>
-    <t>Mergen the Learned</t>
-  </si>
-  <si>
-    <t>Quetzalcoatl</t>
-  </si>
-  <si>
-    <t>Tayne</t>
-  </si>
-  <si>
-    <t>Weaver</t>
-  </si>
-  <si>
-    <t>Havelock</t>
-  </si>
-  <si>
-    <t>“Granite” Halsey</t>
-  </si>
-  <si>
-    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/The Hated - Little Chaos_CardFrontImage.png</t>
-  </si>
-  <si>
-    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Anode - The Melter_CardFrontImage.png</t>
-  </si>
-  <si>
-    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/OBV-64 Oblivion Barge_CardFrontImage.png</t>
-  </si>
-  <si>
-    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/PRK-91 Provenance Ark_CardFrontImage.png</t>
-  </si>
-  <si>
-    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Scanner Tower_CardFrontImage.png</t>
-  </si>
-  <si>
-    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Shield Platform_CardFrontImage.png</t>
-  </si>
-  <si>
-    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Heavy Calibre Orbital Gun_CardFrontImage.png</t>
-  </si>
-  <si>
-    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Leonnatus_CardFrontImage.png</t>
-  </si>
-  <si>
-    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Antigonus_CardFrontImage.png</t>
-  </si>
-  <si>
-    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Seleucus_CardFrontImage.png</t>
-  </si>
-  <si>
-    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Ptolemy_CardFrontImage.png</t>
-  </si>
-  <si>
-    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Antony_CardFrontImage.png</t>
-  </si>
-  <si>
-    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Cato_CardFrontImage.png</t>
-  </si>
-  <si>
-    <t>https:/raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Brutus_CardFrontImage.png</t>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/The Hated - Little Chaos_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Anode - The Melter_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/OBV-64 Oblivion Barge_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/PRK-91_Provenance_Ark_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Scanner Tower_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Shield Platform_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Heavy Calibre Orbital Gun_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Leonnatus_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Antigonus_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Seleucus_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Ptolemy_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Antony_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Cato_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Brutus_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>Gravitational Arc</t>
+  </si>
+  <si>
+    <t>Ghost Orb Tower</t>
+  </si>
+  <si>
+    <t>Sluice</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Syntax</t>
+  </si>
+  <si>
+    <t>Synthesis</t>
+  </si>
+  <si>
+    <t>Sierra</t>
+  </si>
+  <si>
+    <t>Shade</t>
+  </si>
+  <si>
+    <t>Rhiannon Major - Leaden Triad</t>
+  </si>
+  <si>
+    <t>Vanguard 6"</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Gravitational Arc_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Gravitational Arc_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Ghost Orb Tower_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Ghost Orb Tower_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Sluice_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Sluice_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Source_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Source_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Syntax_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Syntax_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Synthesis_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Synthesis_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Sierra_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Sierra_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Shade_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Shade_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Rhiannon Major - Leaden Triad_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Rhiannon Major - Leaden Triad_CardFrontImage.png</t>
   </si>
 </sst>
 </file>
@@ -4454,7 +4538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R363"/>
+  <dimension ref="A1:S372"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -4589,7 +4673,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B3">
         <v>155</v>
@@ -4645,7 +4729,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B4">
         <v>195</v>
@@ -4701,7 +4785,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B5">
         <v>310</v>
@@ -4757,7 +4841,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B6">
         <v>520</v>
@@ -8285,7 +8369,7 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B69">
         <v>207</v>
@@ -8341,7 +8425,7 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="B70">
         <v>200</v>
@@ -8397,7 +8481,7 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="B71">
         <v>310</v>
@@ -8453,7 +8537,7 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B72">
         <v>555</v>
@@ -10304,7 +10388,7 @@
         <v>424</v>
       </c>
       <c r="B105">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C105" t="s">
         <v>198</v>
@@ -11253,7 +11337,7 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="B122">
         <v>158</v>
@@ -11309,7 +11393,7 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B123">
         <v>255</v>
@@ -11365,7 +11449,7 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B124">
         <v>415</v>
@@ -11421,7 +11505,7 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="B125">
         <v>570</v>
@@ -13437,7 +13521,7 @@
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B161">
         <v>170</v>
@@ -13493,7 +13577,7 @@
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B162">
         <v>285</v>
@@ -13549,7 +13633,7 @@
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B163">
         <v>265</v>
@@ -13605,7 +13689,7 @@
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="B164">
         <v>575</v>
@@ -16069,7 +16153,7 @@
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="B208">
         <v>245</v>
@@ -16125,7 +16209,7 @@
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B209">
         <v>195</v>
@@ -16181,7 +16265,7 @@
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B210">
         <v>295</v>
@@ -16237,7 +16321,7 @@
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B211">
         <v>495</v>
@@ -18813,7 +18897,7 @@
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="B257">
         <v>155</v>
@@ -18869,7 +18953,7 @@
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="B258">
         <v>220</v>
@@ -18925,7 +19009,7 @@
     </row>
     <row r="259" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="B259">
         <v>330</v>
@@ -18981,7 +19065,7 @@
     </row>
     <row r="260" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="B260">
         <v>635</v>
@@ -24109,7 +24193,7 @@
         <v>237</v>
       </c>
       <c r="O352" s="2" t="s">
-        <v>1304</v>
+        <v>1338</v>
       </c>
       <c r="P352" s="2" t="s">
         <v>1342</v>
@@ -24121,7 +24205,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="353" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1291</v>
       </c>
@@ -24162,7 +24246,7 @@
         <v>295</v>
       </c>
       <c r="O353" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="P353" s="2" t="s">
         <v>1343</v>
@@ -24174,7 +24258,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="354" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>1292</v>
       </c>
@@ -24215,7 +24299,7 @@
         <v>295</v>
       </c>
       <c r="O354" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="P354" s="2" t="s">
         <v>1344</v>
@@ -24227,7 +24311,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="355" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1293</v>
       </c>
@@ -24268,7 +24352,7 @@
         <v>295</v>
       </c>
       <c r="O355" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="P355" s="2" t="s">
         <v>1345</v>
@@ -24280,7 +24364,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="356" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1294</v>
       </c>
@@ -24321,7 +24405,7 @@
         <v>295</v>
       </c>
       <c r="O356" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="P356" s="2" t="s">
         <v>1346</v>
@@ -24333,7 +24417,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="357" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1295</v>
       </c>
@@ -24377,7 +24461,7 @@
         <v>295</v>
       </c>
       <c r="O357" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="P357" s="2" t="s">
         <v>1347</v>
@@ -24389,7 +24473,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="358" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1294</v>
       </c>
@@ -24430,7 +24514,7 @@
         <v>295</v>
       </c>
       <c r="O358" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="P358" s="2" t="s">
         <v>1346</v>
@@ -24442,7 +24526,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="359" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1297</v>
       </c>
@@ -24483,7 +24567,7 @@
         <v>295</v>
       </c>
       <c r="O359" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="P359" s="2" t="s">
         <v>1348</v>
@@ -24495,7 +24579,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="360" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1298</v>
       </c>
@@ -24536,7 +24620,7 @@
         <v>295</v>
       </c>
       <c r="O360" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="P360" s="2" t="s">
         <v>1349</v>
@@ -24548,7 +24632,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="361" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1299</v>
       </c>
@@ -24589,7 +24673,7 @@
         <v>295</v>
       </c>
       <c r="O361" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="P361" s="2" t="s">
         <v>1350</v>
@@ -24601,7 +24685,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="362" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1300</v>
       </c>
@@ -24642,7 +24726,7 @@
         <v>295</v>
       </c>
       <c r="O362" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="P362" s="2" t="s">
         <v>1351</v>
@@ -24654,7 +24738,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="363" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1301</v>
       </c>
@@ -24694,8 +24778,8 @@
       <c r="N363" t="s">
         <v>295</v>
       </c>
-      <c r="O363" t="s">
-        <v>1314</v>
+      <c r="O363" s="2" t="s">
+        <v>1313</v>
       </c>
       <c r="P363" s="2" t="s">
         <v>1352</v>
@@ -24704,6 +24788,490 @@
         <v>1143</v>
       </c>
       <c r="R363" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="364" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D364">
+        <v>30</v>
+      </c>
+      <c r="E364">
+        <v>0</v>
+      </c>
+      <c r="F364">
+        <v>8</v>
+      </c>
+      <c r="G364">
+        <v>0</v>
+      </c>
+      <c r="H364">
+        <v>0</v>
+      </c>
+      <c r="I364">
+        <v>4</v>
+      </c>
+      <c r="J364">
+        <v>4</v>
+      </c>
+      <c r="K364">
+        <v>0</v>
+      </c>
+      <c r="L364">
+        <v>1</v>
+      </c>
+      <c r="N364" t="s">
+        <v>16</v>
+      </c>
+      <c r="O364" t="s">
+        <v>1363</v>
+      </c>
+      <c r="P364" t="s">
+        <v>1364</v>
+      </c>
+      <c r="Q364" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R364" t="s">
+        <v>1143</v>
+      </c>
+      <c r="S364" s="2"/>
+    </row>
+    <row r="365" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D365">
+        <v>30</v>
+      </c>
+      <c r="E365">
+        <v>0</v>
+      </c>
+      <c r="F365">
+        <v>8</v>
+      </c>
+      <c r="G365">
+        <v>0</v>
+      </c>
+      <c r="H365">
+        <v>0</v>
+      </c>
+      <c r="I365">
+        <v>4</v>
+      </c>
+      <c r="J365">
+        <v>4</v>
+      </c>
+      <c r="K365">
+        <v>0</v>
+      </c>
+      <c r="L365">
+        <v>1</v>
+      </c>
+      <c r="N365" t="s">
+        <v>16</v>
+      </c>
+      <c r="O365" t="s">
+        <v>1365</v>
+      </c>
+      <c r="P365" t="s">
+        <v>1366</v>
+      </c>
+      <c r="Q365" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R365" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="366" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B366">
+        <v>152</v>
+      </c>
+      <c r="C366" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D366">
+        <v>50</v>
+      </c>
+      <c r="E366">
+        <v>7</v>
+      </c>
+      <c r="F366">
+        <v>10</v>
+      </c>
+      <c r="G366">
+        <v>4</v>
+      </c>
+      <c r="H366">
+        <v>11</v>
+      </c>
+      <c r="I366">
+        <v>4</v>
+      </c>
+      <c r="J366">
+        <v>4</v>
+      </c>
+      <c r="K366">
+        <v>5</v>
+      </c>
+      <c r="L366">
+        <v>1</v>
+      </c>
+      <c r="N366" t="s">
+        <v>16</v>
+      </c>
+      <c r="O366" t="s">
+        <v>1367</v>
+      </c>
+      <c r="P366" t="s">
+        <v>1368</v>
+      </c>
+      <c r="Q366" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R366" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="367" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B367">
+        <v>190</v>
+      </c>
+      <c r="C367" t="s">
+        <v>198</v>
+      </c>
+      <c r="D367">
+        <v>50</v>
+      </c>
+      <c r="E367">
+        <v>8</v>
+      </c>
+      <c r="F367">
+        <v>10</v>
+      </c>
+      <c r="G367">
+        <v>4</v>
+      </c>
+      <c r="H367">
+        <v>12</v>
+      </c>
+      <c r="I367">
+        <v>4</v>
+      </c>
+      <c r="J367">
+        <v>4</v>
+      </c>
+      <c r="K367">
+        <v>5</v>
+      </c>
+      <c r="L367">
+        <v>1</v>
+      </c>
+      <c r="M367" t="s">
+        <v>1362</v>
+      </c>
+      <c r="N367" t="s">
+        <v>16</v>
+      </c>
+      <c r="O367" t="s">
+        <v>1369</v>
+      </c>
+      <c r="P367" t="s">
+        <v>1370</v>
+      </c>
+      <c r="Q367" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R367" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="368" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B368">
+        <v>175</v>
+      </c>
+      <c r="C368" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D368">
+        <v>50</v>
+      </c>
+      <c r="E368">
+        <v>8</v>
+      </c>
+      <c r="F368">
+        <v>10</v>
+      </c>
+      <c r="G368">
+        <v>4</v>
+      </c>
+      <c r="H368">
+        <v>14</v>
+      </c>
+      <c r="I368">
+        <v>4</v>
+      </c>
+      <c r="J368">
+        <v>4</v>
+      </c>
+      <c r="K368">
+        <v>5</v>
+      </c>
+      <c r="L368">
+        <v>1</v>
+      </c>
+      <c r="N368" t="s">
+        <v>16</v>
+      </c>
+      <c r="O368" t="s">
+        <v>1371</v>
+      </c>
+      <c r="P368" t="s">
+        <v>1372</v>
+      </c>
+      <c r="Q368" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R368" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="369" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B369">
+        <v>230</v>
+      </c>
+      <c r="C369" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D369">
+        <v>50</v>
+      </c>
+      <c r="E369">
+        <v>8</v>
+      </c>
+      <c r="F369">
+        <v>10</v>
+      </c>
+      <c r="G369">
+        <v>4</v>
+      </c>
+      <c r="H369">
+        <v>14</v>
+      </c>
+      <c r="I369">
+        <v>4</v>
+      </c>
+      <c r="J369">
+        <v>4</v>
+      </c>
+      <c r="K369">
+        <v>5</v>
+      </c>
+      <c r="L369">
+        <v>1</v>
+      </c>
+      <c r="N369" t="s">
+        <v>16</v>
+      </c>
+      <c r="O369" t="s">
+        <v>1373</v>
+      </c>
+      <c r="P369" t="s">
+        <v>1374</v>
+      </c>
+      <c r="Q369" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R369" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="370" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B370">
+        <v>185</v>
+      </c>
+      <c r="C370" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D370">
+        <v>50</v>
+      </c>
+      <c r="E370">
+        <v>8</v>
+      </c>
+      <c r="F370">
+        <v>10</v>
+      </c>
+      <c r="G370">
+        <v>4</v>
+      </c>
+      <c r="H370">
+        <v>14</v>
+      </c>
+      <c r="I370">
+        <v>4</v>
+      </c>
+      <c r="J370">
+        <v>4</v>
+      </c>
+      <c r="K370">
+        <v>5</v>
+      </c>
+      <c r="L370">
+        <v>1</v>
+      </c>
+      <c r="N370" t="s">
+        <v>16</v>
+      </c>
+      <c r="O370" t="s">
+        <v>1375</v>
+      </c>
+      <c r="P370" t="s">
+        <v>1376</v>
+      </c>
+      <c r="Q370" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R370" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="371" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B371">
+        <v>225</v>
+      </c>
+      <c r="C371" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D371">
+        <v>50</v>
+      </c>
+      <c r="E371">
+        <v>8</v>
+      </c>
+      <c r="F371">
+        <v>10</v>
+      </c>
+      <c r="G371">
+        <v>4</v>
+      </c>
+      <c r="H371">
+        <v>14</v>
+      </c>
+      <c r="I371">
+        <v>4</v>
+      </c>
+      <c r="J371">
+        <v>4</v>
+      </c>
+      <c r="K371">
+        <v>5</v>
+      </c>
+      <c r="L371">
+        <v>1</v>
+      </c>
+      <c r="N371" t="s">
+        <v>16</v>
+      </c>
+      <c r="O371" t="s">
+        <v>1377</v>
+      </c>
+      <c r="P371" t="s">
+        <v>1378</v>
+      </c>
+      <c r="Q371" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R371" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="372" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B372">
+        <v>71</v>
+      </c>
+      <c r="C372" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D372">
+        <v>30</v>
+      </c>
+      <c r="E372">
+        <v>8</v>
+      </c>
+      <c r="F372">
+        <v>6</v>
+      </c>
+      <c r="G372">
+        <v>4</v>
+      </c>
+      <c r="H372">
+        <v>6</v>
+      </c>
+      <c r="I372">
+        <v>3</v>
+      </c>
+      <c r="J372">
+        <v>4</v>
+      </c>
+      <c r="K372">
+        <v>6</v>
+      </c>
+      <c r="L372">
+        <v>1</v>
+      </c>
+      <c r="M372" t="s">
+        <v>1258</v>
+      </c>
+      <c r="N372" t="s">
+        <v>941</v>
+      </c>
+      <c r="O372" t="s">
+        <v>1379</v>
+      </c>
+      <c r="P372" t="s">
+        <v>1380</v>
+      </c>
+      <c r="Q372" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R372" t="s">
         <v>1143</v>
       </c>
     </row>
@@ -24746,11 +25314,25 @@
     <hyperlink ref="O325" r:id="rId35" xr:uid="{DE2F7D83-9AEF-45C0-BC31-FEBEFD8A07DE}"/>
     <hyperlink ref="P321" r:id="rId36" xr:uid="{02117735-8EBF-4917-BE94-6ADA5B7F51C3}"/>
     <hyperlink ref="O349" r:id="rId37" xr:uid="{0391698A-2426-4118-8FD5-B4AF7E613286}"/>
-    <hyperlink ref="P349" r:id="rId38" display="https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/The Hated - Little Chaos_CardFrontImage.png" xr:uid="{E9767834-A49F-47F2-AF9F-55B221D57C59}"/>
-    <hyperlink ref="P350" r:id="rId39" display="https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips//BIO/Anode - The Melter_CardFrontImage.png" xr:uid="{01F86FA8-D3B1-47E3-A22B-9BCE334EB3FE}"/>
+    <hyperlink ref="P349" r:id="rId38" xr:uid="{E9767834-A49F-47F2-AF9F-55B221D57C59}"/>
+    <hyperlink ref="P350" r:id="rId39" xr:uid="{01F86FA8-D3B1-47E3-A22B-9BCE334EB3FE}"/>
     <hyperlink ref="O350" r:id="rId40" xr:uid="{E4D87E9E-ECDF-4D05-9366-677CBA028E23}"/>
     <hyperlink ref="P351:P363" r:id="rId41" display="https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/BIO/Anode - The Melter_ModelImage.png" xr:uid="{3CC59D09-23DB-4265-BAD0-94C03FC344FF}"/>
     <hyperlink ref="O352" r:id="rId42" xr:uid="{E8A9C9F7-8738-4A01-9CB8-A521C52E00EB}"/>
+    <hyperlink ref="P351" r:id="rId43" xr:uid="{EFEC30FB-6985-40FF-A8C4-5670EC7C93D7}"/>
+    <hyperlink ref="P352" r:id="rId44" xr:uid="{8243F669-633F-423F-A04A-DA24E14CDE48}"/>
+    <hyperlink ref="P353" r:id="rId45" xr:uid="{714E468B-2CA7-4065-9C97-934A6508520C}"/>
+    <hyperlink ref="P354" r:id="rId46" xr:uid="{F0C7B9DA-4735-4B4E-851D-73EE71D0B977}"/>
+    <hyperlink ref="P355" r:id="rId47" xr:uid="{38AE6957-A785-496D-B8B9-4086D5244283}"/>
+    <hyperlink ref="P356" r:id="rId48" xr:uid="{47BA110F-3BBE-495F-B838-3B285D8C3638}"/>
+    <hyperlink ref="P357" r:id="rId49" xr:uid="{F1F487B0-F7E4-4F36-AEBE-E362F6FA71CA}"/>
+    <hyperlink ref="P358" r:id="rId50" xr:uid="{6CBC26E4-7D46-4A79-B1F4-7F310FE5B9BF}"/>
+    <hyperlink ref="P359" r:id="rId51" xr:uid="{E3CD874F-D16A-42C6-962A-1020C03E75E3}"/>
+    <hyperlink ref="P360" r:id="rId52" xr:uid="{17C75E7A-2884-4D18-AA47-F618AEBAB260}"/>
+    <hyperlink ref="P361" r:id="rId53" xr:uid="{1E75A871-D27E-44FF-B60C-29AC3DDFAF86}"/>
+    <hyperlink ref="P362" r:id="rId54" xr:uid="{C4B2BE06-F9BD-4591-AB08-CA5FB4DF8742}"/>
+    <hyperlink ref="P363" r:id="rId55" xr:uid="{AF7B3906-DEAF-400C-9C29-8B3D3010F9AF}"/>
+    <hyperlink ref="O363" r:id="rId56" xr:uid="{9F4E4532-365D-4D58-8552-DCE414A279AE}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Test Code/OneAsMany/d.xlsx
+++ b/Test Code/OneAsMany/d.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DropFleetTTS_Repo\DropfleetTTS\Test Code\OneAsMany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FEDE5B8-A30C-4CFE-9B44-DB49FDADDFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780CBDDE-D2E9-49A2-A986-8D3C265F2EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1845" yWindow="1095" windowWidth="30165" windowHeight="19350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Ship Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ship Data'!$A$1:$P$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ship Data'!$A$1:$R$384</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5420" uniqueCount="1381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5512" uniqueCount="1419">
   <si>
     <t>Name</t>
   </si>
@@ -4179,6 +4179,120 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Rhiannon Major - Leaden Triad_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>Skybane Halo</t>
+  </si>
+  <si>
+    <t>Shrouding Platform</t>
+  </si>
+  <si>
+    <t>Infestation Bastion</t>
+  </si>
+  <si>
+    <t>Nereid</t>
+  </si>
+  <si>
+    <t>Rusalka</t>
+  </si>
+  <si>
+    <t>Nixie</t>
+  </si>
+  <si>
+    <t>Gloam</t>
+  </si>
+  <si>
+    <t>Cloak-1, Stealth, Vanguard-6"</t>
+  </si>
+  <si>
+    <t>Kikimora</t>
+  </si>
+  <si>
+    <t>Bannik</t>
+  </si>
+  <si>
+    <t>Command Ship 1</t>
+  </si>
+  <si>
+    <t>Melusine</t>
+  </si>
+  <si>
+    <t>Fossegrim</t>
+  </si>
+  <si>
+    <t>Avram Bei - Subatomic</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Avram Bei - Subatomic_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Avram Bei - Subatomic_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Skybane Halo_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Skybane Halo_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Shrouding Platform_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Shrouding Platform_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Infestation Bastion_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Infestation Bastion_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Nereid_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Nereid_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Rusalka_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Rusalka_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Nixie_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Nixie_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Gloam_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Gloam_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Kikimora_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Kikimora_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Bannik_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Bannik_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Melusine_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Melusine_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Fossegrim_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Fossegrim_CardFrontImage.png</t>
   </si>
 </sst>
 </file>
@@ -4538,7 +4652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S372"/>
+  <dimension ref="A1:S384"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -15372,7 +15486,7 @@
         <v>734</v>
       </c>
       <c r="B194">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C194" t="s">
         <v>198</v>
@@ -15428,7 +15542,7 @@
         <v>737</v>
       </c>
       <c r="B195">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C195" t="s">
         <v>198</v>
@@ -25206,7 +25320,7 @@
       <c r="N371" t="s">
         <v>16</v>
       </c>
-      <c r="O371" t="s">
+      <c r="O371" s="2" t="s">
         <v>1377</v>
       </c>
       <c r="P371" t="s">
@@ -25262,10 +25376,10 @@
       <c r="N372" t="s">
         <v>941</v>
       </c>
-      <c r="O372" t="s">
+      <c r="O372" s="2" t="s">
         <v>1379</v>
       </c>
-      <c r="P372" t="s">
+      <c r="P372" s="2" t="s">
         <v>1380</v>
       </c>
       <c r="Q372" t="s">
@@ -25275,7 +25389,668 @@
         <v>1143</v>
       </c>
     </row>
+    <row r="373" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D373">
+        <v>30</v>
+      </c>
+      <c r="E373">
+        <v>0</v>
+      </c>
+      <c r="F373">
+        <v>8</v>
+      </c>
+      <c r="G373">
+        <v>0</v>
+      </c>
+      <c r="H373">
+        <v>0</v>
+      </c>
+      <c r="I373">
+        <v>4</v>
+      </c>
+      <c r="J373">
+        <v>5</v>
+      </c>
+      <c r="K373">
+        <v>0</v>
+      </c>
+      <c r="L373">
+        <v>0</v>
+      </c>
+      <c r="M373" t="s">
+        <v>974</v>
+      </c>
+      <c r="N373" t="s">
+        <v>621</v>
+      </c>
+      <c r="O373" t="s">
+        <v>1397</v>
+      </c>
+      <c r="P373" t="s">
+        <v>1398</v>
+      </c>
+      <c r="Q373" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R373" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="374" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D374">
+        <v>30</v>
+      </c>
+      <c r="E374">
+        <v>0</v>
+      </c>
+      <c r="F374">
+        <v>6</v>
+      </c>
+      <c r="G374">
+        <v>0</v>
+      </c>
+      <c r="H374">
+        <v>0</v>
+      </c>
+      <c r="I374">
+        <v>5</v>
+      </c>
+      <c r="J374">
+        <v>5</v>
+      </c>
+      <c r="K374">
+        <v>0</v>
+      </c>
+      <c r="L374">
+        <v>0</v>
+      </c>
+      <c r="N374" t="s">
+        <v>621</v>
+      </c>
+      <c r="O374" t="s">
+        <v>1399</v>
+      </c>
+      <c r="P374" t="s">
+        <v>1400</v>
+      </c>
+      <c r="Q374" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R374" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="375" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D375">
+        <v>30</v>
+      </c>
+      <c r="E375">
+        <v>0</v>
+      </c>
+      <c r="F375">
+        <v>0</v>
+      </c>
+      <c r="G375">
+        <v>0</v>
+      </c>
+      <c r="H375">
+        <v>0</v>
+      </c>
+      <c r="I375">
+        <v>5</v>
+      </c>
+      <c r="J375">
+        <v>5</v>
+      </c>
+      <c r="K375">
+        <v>0</v>
+      </c>
+      <c r="L375">
+        <v>0</v>
+      </c>
+      <c r="N375" t="s">
+        <v>621</v>
+      </c>
+      <c r="O375" t="s">
+        <v>1401</v>
+      </c>
+      <c r="P375" t="s">
+        <v>1402</v>
+      </c>
+      <c r="Q375" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R375" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="376" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B376">
+        <v>190</v>
+      </c>
+      <c r="C376" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D376">
+        <v>50</v>
+      </c>
+      <c r="E376">
+        <v>8</v>
+      </c>
+      <c r="F376">
+        <v>6</v>
+      </c>
+      <c r="G376">
+        <v>8</v>
+      </c>
+      <c r="H376">
+        <v>13</v>
+      </c>
+      <c r="I376">
+        <v>4</v>
+      </c>
+      <c r="J376">
+        <v>4</v>
+      </c>
+      <c r="K376">
+        <v>6</v>
+      </c>
+      <c r="L376">
+        <v>1</v>
+      </c>
+      <c r="M376" t="s">
+        <v>632</v>
+      </c>
+      <c r="N376" t="s">
+        <v>621</v>
+      </c>
+      <c r="O376" t="s">
+        <v>1403</v>
+      </c>
+      <c r="P376" t="s">
+        <v>1404</v>
+      </c>
+      <c r="Q376" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R376" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="377" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B377">
+        <v>130</v>
+      </c>
+      <c r="C377" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D377">
+        <v>50</v>
+      </c>
+      <c r="E377">
+        <v>8</v>
+      </c>
+      <c r="F377">
+        <v>6</v>
+      </c>
+      <c r="G377">
+        <v>8</v>
+      </c>
+      <c r="H377">
+        <v>13</v>
+      </c>
+      <c r="I377">
+        <v>4</v>
+      </c>
+      <c r="J377">
+        <v>4</v>
+      </c>
+      <c r="K377">
+        <v>6</v>
+      </c>
+      <c r="L377">
+        <v>1</v>
+      </c>
+      <c r="N377" t="s">
+        <v>621</v>
+      </c>
+      <c r="O377" t="s">
+        <v>1405</v>
+      </c>
+      <c r="P377" t="s">
+        <v>1406</v>
+      </c>
+      <c r="Q377" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R377" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="378" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B378">
+        <v>145</v>
+      </c>
+      <c r="C378" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D378">
+        <v>50</v>
+      </c>
+      <c r="E378">
+        <v>8</v>
+      </c>
+      <c r="F378">
+        <v>6</v>
+      </c>
+      <c r="G378">
+        <v>8</v>
+      </c>
+      <c r="H378">
+        <v>13</v>
+      </c>
+      <c r="I378">
+        <v>4</v>
+      </c>
+      <c r="J378">
+        <v>4</v>
+      </c>
+      <c r="K378">
+        <v>6</v>
+      </c>
+      <c r="L378">
+        <v>1</v>
+      </c>
+      <c r="M378" t="s">
+        <v>632</v>
+      </c>
+      <c r="N378" t="s">
+        <v>621</v>
+      </c>
+      <c r="O378" t="s">
+        <v>1407</v>
+      </c>
+      <c r="P378" t="s">
+        <v>1408</v>
+      </c>
+      <c r="Q378" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R378" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="379" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B379">
+        <v>160</v>
+      </c>
+      <c r="C379" t="s">
+        <v>198</v>
+      </c>
+      <c r="D379">
+        <v>50</v>
+      </c>
+      <c r="E379">
+        <v>10</v>
+      </c>
+      <c r="F379">
+        <v>6</v>
+      </c>
+      <c r="G379">
+        <v>8</v>
+      </c>
+      <c r="H379">
+        <v>14</v>
+      </c>
+      <c r="I379">
+        <v>4</v>
+      </c>
+      <c r="J379">
+        <v>4</v>
+      </c>
+      <c r="K379">
+        <v>6</v>
+      </c>
+      <c r="L379">
+        <v>1</v>
+      </c>
+      <c r="M379" t="s">
+        <v>1388</v>
+      </c>
+      <c r="N379" t="s">
+        <v>621</v>
+      </c>
+      <c r="O379" t="s">
+        <v>1409</v>
+      </c>
+      <c r="P379" t="s">
+        <v>1410</v>
+      </c>
+      <c r="Q379" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R379" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="380" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B380">
+        <v>230</v>
+      </c>
+      <c r="C380" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D380">
+        <v>50</v>
+      </c>
+      <c r="E380">
+        <v>8</v>
+      </c>
+      <c r="F380">
+        <v>6</v>
+      </c>
+      <c r="G380">
+        <v>8</v>
+      </c>
+      <c r="H380">
+        <v>15</v>
+      </c>
+      <c r="I380">
+        <v>4</v>
+      </c>
+      <c r="J380">
+        <v>4</v>
+      </c>
+      <c r="K380">
+        <v>5</v>
+      </c>
+      <c r="L380">
+        <v>1</v>
+      </c>
+      <c r="M380" t="s">
+        <v>632</v>
+      </c>
+      <c r="N380" t="s">
+        <v>621</v>
+      </c>
+      <c r="O380" t="s">
+        <v>1411</v>
+      </c>
+      <c r="P380" t="s">
+        <v>1412</v>
+      </c>
+      <c r="Q380" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R380" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="381" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B381">
+        <v>250</v>
+      </c>
+      <c r="C381" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D381">
+        <v>50</v>
+      </c>
+      <c r="E381">
+        <v>8</v>
+      </c>
+      <c r="F381">
+        <v>6</v>
+      </c>
+      <c r="G381">
+        <v>8</v>
+      </c>
+      <c r="H381">
+        <v>15</v>
+      </c>
+      <c r="I381">
+        <v>4</v>
+      </c>
+      <c r="J381">
+        <v>4</v>
+      </c>
+      <c r="K381">
+        <v>5</v>
+      </c>
+      <c r="L381">
+        <v>1</v>
+      </c>
+      <c r="M381" t="s">
+        <v>1391</v>
+      </c>
+      <c r="N381" t="s">
+        <v>621</v>
+      </c>
+      <c r="O381" t="s">
+        <v>1413</v>
+      </c>
+      <c r="P381" t="s">
+        <v>1414</v>
+      </c>
+      <c r="Q381" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R381" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="382" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B382">
+        <v>255</v>
+      </c>
+      <c r="C382" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D382">
+        <v>50</v>
+      </c>
+      <c r="E382">
+        <v>8</v>
+      </c>
+      <c r="F382">
+        <v>6</v>
+      </c>
+      <c r="G382">
+        <v>8</v>
+      </c>
+      <c r="H382">
+        <v>15</v>
+      </c>
+      <c r="I382">
+        <v>4</v>
+      </c>
+      <c r="J382">
+        <v>4</v>
+      </c>
+      <c r="K382">
+        <v>5</v>
+      </c>
+      <c r="L382">
+        <v>1</v>
+      </c>
+      <c r="N382" t="s">
+        <v>621</v>
+      </c>
+      <c r="O382" t="s">
+        <v>1415</v>
+      </c>
+      <c r="P382" t="s">
+        <v>1416</v>
+      </c>
+      <c r="Q382" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R382" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="383" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B383">
+        <v>195</v>
+      </c>
+      <c r="C383" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D383">
+        <v>50</v>
+      </c>
+      <c r="E383">
+        <v>8</v>
+      </c>
+      <c r="F383">
+        <v>6</v>
+      </c>
+      <c r="G383">
+        <v>8</v>
+      </c>
+      <c r="H383">
+        <v>15</v>
+      </c>
+      <c r="I383">
+        <v>4</v>
+      </c>
+      <c r="J383">
+        <v>4</v>
+      </c>
+      <c r="K383">
+        <v>5</v>
+      </c>
+      <c r="L383">
+        <v>1</v>
+      </c>
+      <c r="M383" t="s">
+        <v>632</v>
+      </c>
+      <c r="N383" t="s">
+        <v>621</v>
+      </c>
+      <c r="O383" t="s">
+        <v>1417</v>
+      </c>
+      <c r="P383" t="s">
+        <v>1418</v>
+      </c>
+      <c r="Q383" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R383" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="384" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B384">
+        <v>96</v>
+      </c>
+      <c r="C384" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D384">
+        <v>30</v>
+      </c>
+      <c r="E384">
+        <v>12</v>
+      </c>
+      <c r="F384">
+        <v>8</v>
+      </c>
+      <c r="G384">
+        <v>2</v>
+      </c>
+      <c r="H384">
+        <v>8</v>
+      </c>
+      <c r="I384">
+        <v>4</v>
+      </c>
+      <c r="J384">
+        <v>5</v>
+      </c>
+      <c r="K384">
+        <v>6</v>
+      </c>
+      <c r="L384">
+        <v>1</v>
+      </c>
+      <c r="M384" t="s">
+        <v>1258</v>
+      </c>
+      <c r="N384" t="s">
+        <v>295</v>
+      </c>
+      <c r="O384" t="s">
+        <v>1395</v>
+      </c>
+      <c r="P384" t="s">
+        <v>1396</v>
+      </c>
+      <c r="Q384" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R384" t="s">
+        <v>1143</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:R384" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="O69" r:id="rId1" xr:uid="{199D85C6-8205-44AF-8889-1D194BB490BD}"/>
     <hyperlink ref="O70" r:id="rId2" xr:uid="{4C94DFDA-489B-476E-8AC6-E7F89E79353B}"/>
@@ -25333,6 +26108,9 @@
     <hyperlink ref="P362" r:id="rId54" xr:uid="{C4B2BE06-F9BD-4591-AB08-CA5FB4DF8742}"/>
     <hyperlink ref="P363" r:id="rId55" xr:uid="{AF7B3906-DEAF-400C-9C29-8B3D3010F9AF}"/>
     <hyperlink ref="O363" r:id="rId56" xr:uid="{9F4E4532-365D-4D58-8552-DCE414A279AE}"/>
+    <hyperlink ref="O371" r:id="rId57" xr:uid="{E0109082-30EB-4A82-BD69-548573A33E7F}"/>
+    <hyperlink ref="O372" r:id="rId58" xr:uid="{EAA5CE92-18AE-4283-AB59-32876BFD300C}"/>
+    <hyperlink ref="P372" r:id="rId59" xr:uid="{C6EE6FC9-DEB2-4117-937A-5F1F2737EB26}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
